--- a/Data_Students/Students_2025_2026_Edition_July2025.xlsx
+++ b/Data_Students/Students_2025_2026_Edition_July2025.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="746" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="746" uniqueCount="157">
   <si>
     <t>S1 (Undergraduate)</t>
   </si>
@@ -456,9 +456,6 @@
   </si>
   <si>
     <t>Technological University of the Shannon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technological University of the Shannon </t>
   </si>
   <si>
     <t>Social Sciences &amp; Politics</t>
@@ -853,7 +850,7 @@
         <v>123</v>
       </c>
       <c r="G1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H1" t="s">
         <v>124</v>
@@ -885,7 +882,7 @@
         <v>4</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H2" t="s">
         <v>2</v>
@@ -918,7 +915,7 @@
         <v>4</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H3" t="s">
         <v>3</v>
@@ -951,7 +948,7 @@
         <v>4</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H4" t="s">
         <v>5</v>
@@ -984,7 +981,7 @@
         <v>9</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H5" t="s">
         <v>10</v>
@@ -1017,7 +1014,7 @@
         <v>11</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H6" t="s">
         <v>12</v>
@@ -1083,7 +1080,7 @@
         <v>9</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H8" t="s">
         <v>16</v>
@@ -1149,7 +1146,7 @@
         <v>4</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H10" t="s">
         <v>18</v>
@@ -1182,7 +1179,7 @@
         <v>4</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H11" t="s">
         <v>19</v>
@@ -1215,7 +1212,7 @@
         <v>21</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H12" t="s">
         <v>22</v>
@@ -1248,7 +1245,7 @@
         <v>24</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H13" t="s">
         <v>25</v>
@@ -1281,7 +1278,7 @@
         <v>21</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H14" t="s">
         <v>26</v>
@@ -1314,7 +1311,7 @@
         <v>24</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H15" t="s">
         <v>28</v>
@@ -1347,7 +1344,7 @@
         <v>4</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H16" t="s">
         <v>29</v>
@@ -1380,7 +1377,7 @@
         <v>143</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H17" t="s">
         <v>31</v>
@@ -1413,7 +1410,7 @@
         <v>139</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H18" t="s">
         <v>32</v>
@@ -1446,7 +1443,7 @@
         <v>21</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H19" t="s">
         <v>33</v>
@@ -1479,7 +1476,7 @@
         <v>140</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H20" t="s">
         <v>35</v>
@@ -1512,7 +1509,7 @@
         <v>4</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H21" t="s">
         <v>36</v>
@@ -1545,7 +1542,7 @@
         <v>11</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H22" t="s">
         <v>38</v>
@@ -1578,7 +1575,7 @@
         <v>4</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H23" t="s">
         <v>40</v>
@@ -1611,7 +1608,7 @@
         <v>9</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H24" t="s">
         <v>16</v>
@@ -1644,7 +1641,7 @@
         <v>11</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H25" t="s">
         <v>41</v>
@@ -1677,7 +1674,7 @@
         <v>24</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H26" t="s">
         <v>42</v>
@@ -1710,7 +1707,7 @@
         <v>43</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H27" t="s">
         <v>44</v>
@@ -1743,7 +1740,7 @@
         <v>4</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H28" t="s">
         <v>46</v>
@@ -1776,7 +1773,7 @@
         <v>141</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H29" t="s">
         <v>48</v>
@@ -1809,7 +1806,7 @@
         <v>24</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H30" t="s">
         <v>49</v>
@@ -1875,7 +1872,7 @@
         <v>21</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H32" t="s">
         <v>51</v>
@@ -1908,7 +1905,7 @@
         <v>11</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H33" t="s">
         <v>53</v>
@@ -1941,7 +1938,7 @@
         <v>11</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H34" t="s">
         <v>54</v>
@@ -1974,7 +1971,7 @@
         <v>55</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H35" t="s">
         <v>56</v>
@@ -2007,7 +2004,7 @@
         <v>11</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H36" t="s">
         <v>54</v>
@@ -2040,7 +2037,7 @@
         <v>4</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H37" t="s">
         <v>58</v>
@@ -2073,7 +2070,7 @@
         <v>4</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H38" t="s">
         <v>59</v>
@@ -2106,7 +2103,7 @@
         <v>4</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H39" t="s">
         <v>60</v>
@@ -2139,7 +2136,7 @@
         <v>140</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H40" t="s">
         <v>61</v>
@@ -2172,7 +2169,7 @@
         <v>4</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H41" t="s">
         <v>62</v>
@@ -2205,7 +2202,7 @@
         <v>4</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H42" t="s">
         <v>63</v>
@@ -2235,10 +2232,10 @@
         <v>30</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H43" t="s">
         <v>64</v>
@@ -2271,7 +2268,7 @@
         <v>4</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H44" t="s">
         <v>65</v>
@@ -2304,7 +2301,7 @@
         <v>11</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H45" t="s">
         <v>66</v>
@@ -2370,7 +2367,7 @@
         <v>4</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H47" t="s">
         <v>68</v>
@@ -2403,7 +2400,7 @@
         <v>4</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H48" t="s">
         <v>69</v>
@@ -2436,7 +2433,7 @@
         <v>4</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H49" t="s">
         <v>70</v>
@@ -2469,7 +2466,7 @@
         <v>4</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H50" t="s">
         <v>71</v>
@@ -2502,7 +2499,7 @@
         <v>24</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H51" t="s">
         <v>72</v>
@@ -2535,7 +2532,7 @@
         <v>24</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H52" t="s">
         <v>73</v>
@@ -2568,7 +2565,7 @@
         <v>4</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H53" t="s">
         <v>74</v>
@@ -2601,7 +2598,7 @@
         <v>4</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H54" t="s">
         <v>76</v>
@@ -2634,7 +2631,7 @@
         <v>11</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H55" t="s">
         <v>77</v>
@@ -2667,7 +2664,7 @@
         <v>11</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H56" t="s">
         <v>78</v>
@@ -2700,7 +2697,7 @@
         <v>79</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H57" t="s">
         <v>80</v>
@@ -2733,7 +2730,7 @@
         <v>4</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H58" t="s">
         <v>81</v>
@@ -2766,7 +2763,7 @@
         <v>21</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H59" t="s">
         <v>82</v>
@@ -2832,7 +2829,7 @@
         <v>142</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H61" t="s">
         <v>84</v>
@@ -2865,7 +2862,7 @@
         <v>4</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H62" t="s">
         <v>85</v>
@@ -2898,7 +2895,7 @@
         <v>4</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H63" t="s">
         <v>86</v>
@@ -2931,7 +2928,7 @@
         <v>4</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H64" t="s">
         <v>87</v>
@@ -2964,7 +2961,7 @@
         <v>89</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H65" t="s">
         <v>90</v>
@@ -2997,7 +2994,7 @@
         <v>24</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H66" t="s">
         <v>91</v>
@@ -3030,7 +3027,7 @@
         <v>4</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H67" t="s">
         <v>92</v>
@@ -3063,7 +3060,7 @@
         <v>11</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H68" t="s">
         <v>44</v>
@@ -3096,7 +3093,7 @@
         <v>4</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H69" t="s">
         <v>93</v>
@@ -3129,7 +3126,7 @@
         <v>9</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H70" t="s">
         <v>94</v>
@@ -3162,7 +3159,7 @@
         <v>4</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H71" t="s">
         <v>5</v>
@@ -3195,7 +3192,7 @@
         <v>9</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H72" t="s">
         <v>87</v>
@@ -3228,7 +3225,7 @@
         <v>95</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H73" t="s">
         <v>96</v>
@@ -3261,7 +3258,7 @@
         <v>21</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H74" t="s">
         <v>97</v>
@@ -3294,7 +3291,7 @@
         <v>11</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H75" t="s">
         <v>46</v>
@@ -3327,7 +3324,7 @@
         <v>98</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H76" t="s">
         <v>99</v>
@@ -3360,7 +3357,7 @@
         <v>11</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H77" t="s">
         <v>100</v>
@@ -3393,7 +3390,7 @@
         <v>9</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H78" t="s">
         <v>101</v>
@@ -3426,7 +3423,7 @@
         <v>4</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H79" t="s">
         <v>102</v>
@@ -3459,7 +3456,7 @@
         <v>24</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H80" t="s">
         <v>104</v>
@@ -3492,7 +3489,7 @@
         <v>11</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H81" t="s">
         <v>106</v>
@@ -3525,7 +3522,7 @@
         <v>24</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H82" t="s">
         <v>107</v>
@@ -3558,7 +3555,7 @@
         <v>4</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H83" t="s">
         <v>108</v>
@@ -3591,7 +3588,7 @@
         <v>4</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H84" t="s">
         <v>109</v>
@@ -3624,7 +3621,7 @@
         <v>4</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H85" t="s">
         <v>110</v>
@@ -3657,7 +3654,7 @@
         <v>4</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H86" t="s">
         <v>111</v>
@@ -3690,7 +3687,7 @@
         <v>4</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H87" t="s">
         <v>112</v>
@@ -3723,7 +3720,7 @@
         <v>4</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H88" t="s">
         <v>113</v>
@@ -3756,7 +3753,7 @@
         <v>4</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H89" t="s">
         <v>114</v>
@@ -3789,7 +3786,7 @@
         <v>4</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H90" t="s">
         <v>115</v>
@@ -3822,7 +3819,7 @@
         <v>4</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H91" t="s">
         <v>116</v>
@@ -3855,7 +3852,7 @@
         <v>4</v>
       </c>
       <c r="G92" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H92" t="s">
         <v>86</v>
@@ -3888,7 +3885,7 @@
         <v>4</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H93" t="s">
         <v>117</v>
